--- a/figures/FMNIST/tables/window_size/noise_fashion_v1_delta_fashion_v2/results.xlsx
+++ b/figures/FMNIST/tables/window_size/noise_fashion_v1_delta_fashion_v2/results.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciek\Documents\GitHub\MUNDataStream\figures\FMNIST\tables\window_size\noise_fashion_v1_delta_fashion_v2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684534F2-A237-4609-BED3-EA5C6F5821A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4650" yWindow="5730" windowWidth="28800" windowHeight="15885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="accuracy" sheetId="1" r:id="rId1"/>
     <sheet name="recovery_time" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>window_size</t>
   </si>
@@ -35,17 +41,14 @@
     <t>accuracy_recovery_time</t>
   </si>
   <si>
-    <t>mean_memory</t>
-  </si>
-  <si>
     <t>mean_time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,17 +107,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2007–2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -152,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2007–2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -186,6 +197,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -220,9 +232,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2007–2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,11 +408,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,77 +426,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.8376504297994268</v>
+        <v>0.83765042979942683</v>
       </c>
       <c r="C2">
-        <v>0.7794683908045977</v>
+        <v>0.77946839080459773</v>
       </c>
       <c r="D2">
-        <v>0.8954999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>0.89549999999999985</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.8417717287488061</v>
+        <v>0.84177172874880613</v>
       </c>
       <c r="C3">
         <v>0.7876915708812261</v>
       </c>
       <c r="D3">
-        <v>0.8955428571428571</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>0.89554285714285708</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.8457831900668578</v>
+        <v>0.84578319006685776</v>
       </c>
       <c r="C4">
-        <v>0.7951340996168582</v>
+        <v>0.79513409961685821</v>
       </c>
       <c r="D4">
-        <v>0.8961428571428571</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>0.89614285714285713</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.8454823304680038</v>
+        <v>0.84548233046800381</v>
       </c>
       <c r="C5">
         <v>0.7974521072796934</v>
       </c>
       <c r="D5">
-        <v>0.8932380952380953</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0.89323809523809528</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.8536628462273161</v>
+        <v>0.85366284622731614</v>
       </c>
       <c r="C6">
-        <v>0.80794061302682</v>
+        <v>0.80794061302681996</v>
       </c>
       <c r="D6">
-        <v>0.8991238095238095</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>0.89912380952380955</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9</v>
       </c>
@@ -491,69 +504,69 @@
         <v>0.8448662846227315</v>
       </c>
       <c r="C7">
-        <v>0.800095785440613</v>
+        <v>0.80009578544061299</v>
       </c>
       <c r="D7">
-        <v>0.8893809523809523</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>0.88938095238095227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
       <c r="B8">
-        <v>0.8564278892072589</v>
+        <v>0.85642788920725887</v>
       </c>
       <c r="C8">
-        <v>0.8147892720306513</v>
+        <v>0.81478927203065132</v>
       </c>
       <c r="D8">
-        <v>0.8978285714285714</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>0.89782857142857142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0.8563801337153772</v>
+        <v>0.85638013371537725</v>
       </c>
       <c r="C9">
-        <v>0.8132758620689655</v>
+        <v>0.81327586206896552</v>
       </c>
       <c r="D9">
-        <v>0.8992380952380953</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>0.89923809523809528</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.8626599808978033</v>
+        <v>0.86265998089780327</v>
       </c>
       <c r="C10">
         <v>0.8226724137931033</v>
       </c>
       <c r="D10">
-        <v>0.9024190476190476</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>0.90241904761904757</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.8612989493791786</v>
+        <v>0.86129894937917861</v>
       </c>
       <c r="C11">
-        <v>0.819243295019157</v>
+        <v>0.81924329501915705</v>
       </c>
       <c r="D11">
-        <v>0.9031142857142856</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>0.90311428571428565</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -561,38 +574,38 @@
         <v>0.8643982808022922</v>
       </c>
       <c r="C12">
-        <v>0.8272126436781609</v>
+        <v>0.82721264367816094</v>
       </c>
       <c r="D12">
-        <v>0.9013714285714285</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>0.90137142857142849</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.8651289398280801</v>
+        <v>0.86512893982808015</v>
       </c>
       <c r="C13">
-        <v>0.8258045977011494</v>
+        <v>0.82580459770114945</v>
       </c>
       <c r="D13">
-        <v>0.9042285714285714</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>0.90422857142857138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.8691404011461318</v>
+        <v>0.86914040114613178</v>
       </c>
       <c r="C14">
-        <v>0.8349808429118775</v>
+        <v>0.83498084291187746</v>
       </c>
       <c r="D14">
-        <v>0.9031047619047619</v>
+        <v>0.90310476190476185</v>
       </c>
     </row>
   </sheetData>
@@ -601,11 +614,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,11 +628,8 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -627,13 +637,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>2504389.684813754</v>
-      </c>
-      <c r="D2">
-        <v>2.234837411373927</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>2.2348374113739271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
@@ -641,13 +648,10 @@
         <v>13.66666666666667</v>
       </c>
       <c r="C3">
-        <v>3125982.808022922</v>
-      </c>
-      <c r="D3">
-        <v>2.219014573398278</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>2.2190145733982778</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
@@ -655,13 +659,10 @@
         <v>15.66666666666667</v>
       </c>
       <c r="C4">
-        <v>3745774.212034384</v>
-      </c>
-      <c r="D4">
-        <v>2.190568243347663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>2.1905682433476632</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
@@ -669,13 +670,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>4363763.896848137</v>
-      </c>
-      <c r="D5">
         <v>2.200254289821399</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
@@ -683,13 +681,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>4979951.862464183</v>
-      </c>
-      <c r="D6">
-        <v>2.136342805538681</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>2.1363428055386811</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9</v>
       </c>
@@ -697,27 +692,21 @@
         <v>13.66666666666667</v>
       </c>
       <c r="C7">
-        <v>5594338.108882521</v>
-      </c>
-      <c r="D7">
         <v>2.176692454546334</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
       <c r="B8">
-        <v>17.33333333333333</v>
+        <v>17.333333333333329</v>
       </c>
       <c r="C8">
-        <v>6206922.636103152</v>
-      </c>
-      <c r="D8">
-        <v>2.02255909762465</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>2.0225590976246499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11</v>
       </c>
@@ -725,13 +714,10 @@
         <v>13.33333333333333</v>
       </c>
       <c r="C9">
-        <v>6817705.444126074</v>
-      </c>
-      <c r="D9">
-        <v>2.165187213368685</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>2.1651872133686849</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
@@ -739,13 +725,10 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>7426686.532951291</v>
-      </c>
-      <c r="D10">
-        <v>2.049674786988542</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>2.0496747869885419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
@@ -753,13 +736,10 @@
         <v>13.66666666666667</v>
       </c>
       <c r="C11">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D11">
-        <v>2.14324179547468</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>2.1432417954746801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -767,13 +747,10 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>8639243.553008595</v>
-      </c>
-      <c r="D12">
         <v>2.074887849949377</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
@@ -781,13 +758,10 @@
         <v>14</v>
       </c>
       <c r="C13">
-        <v>9242819.484240688</v>
-      </c>
-      <c r="D13">
         <v>2.121988630421197</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -795,10 +769,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="C14">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D14">
-        <v>6.271977036589309</v>
+        <v>6.2719770365893091</v>
       </c>
     </row>
   </sheetData>
